--- a/astro-site/public/dl/burger-joint-checklist-templates/04-burger-shop-duties-by-role.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/04-burger-shop-duties-by-role.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F9" s="28" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Store leftover beef labeled: raw ground beef covered, date-marked, 41 °F or below, bottom shelf below ready-to-eat food (FDA 3-302.11)</t>
+          <t>Store leftover beef labeled: raw ground beef covered, date-marked, 41 °F or below, below ready-to-eat food and above any raw chicken (FDA 3-302.11)</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -2094,9 +2094,9 @@
       <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Turn off and clean the fryer</t>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Turn off the fryer; clean the outside once the oil is filtered</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>Filter the oil as the fryer manufacturer says (many filter hot by design, others need to cool first); heat-resistant gloves, apron and goggles</t>
+          <t>Filter the oil as the fryer manufacturer says (built-in filtration: with the oil still hot; portable filter: once it has cooled to what the manual allows); heat-resistant gloves, apron and goggles</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
